--- a/logs/tdpcondensateCLIP.xlsx
+++ b/logs/tdpcondensateCLIP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikej\Documents\Career\Georges\Ule\projects\TDPcondensate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikej\Documents\Career\Georges\Ule\intron_retention_propensity\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D855BB8B-5A53-44BC-A52B-8CFD52E8E512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5387B0-B243-46CA-B729-292D4BA1FE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-43305" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="380">
   <si>
     <t>File</t>
   </si>
@@ -1170,7 +1170,13 @@
     <t>GFP-HNRNPA2B1-TDP43_Hs_HEK293_TDPCTD_siT_2_20200812</t>
   </si>
   <si>
-    <t>Column1</t>
+    <t>TDP43_Hs_HEK293_WT_2-5hexandiol_1_20180829</t>
+  </si>
+  <si>
+    <t>TDP43_Hs_HEK293_WT_2-5hexandiol_2_20180829</t>
+  </si>
+  <si>
+    <t>TDP43_Hs_HEK293_WT_2-5hexandiol_3_20180829</t>
   </si>
 </sst>
 </file>
@@ -1233,12 +1239,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1323,14 +1328,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4B71EA4-780D-45DF-B198-8544B00DFBD9}" name="Table1" displayName="Table1" ref="A1:AB67" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
-  <autoFilter ref="A1:AB67" xr:uid="{B4B71EA4-780D-45DF-B198-8544B00DFBD9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AB67">
-    <sortCondition ref="W1:W67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B4B71EA4-780D-45DF-B198-8544B00DFBD9}" name="Table1" displayName="Table1" ref="A1:AA67" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:AA67" xr:uid="{B4B71EA4-780D-45DF-B198-8544B00DFBD9}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA67">
+    <sortCondition ref="V1:V67"/>
   </sortState>
-  <tableColumns count="28">
+  <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{A1C8783A-4DA5-471A-AC34-3A2F9A6A0ECE}" name="File"/>
-    <tableColumn id="28" xr3:uid="{602109F8-32DC-40FD-8C84-39576EE816A9}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{C8B0F116-9C5E-44F6-AA1D-96011D4CF33A}" name="Sample Name" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{049828FD-0E30-41C8-B0C3-77050D49D08B}" name="Project Name"/>
     <tableColumn id="4" xr3:uid="{D13A0063-A6B9-4D6E-BB29-669695DF2B6A}" name="Scientist"/>
@@ -1649,3615 +1653,3612 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB67"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="60.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.85546875" customWidth="1"/>
-    <col min="5" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="40.28515625" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="33.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
-    <col min="12" max="12" width="18.7109375" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" customWidth="1"/>
-    <col min="14" max="14" width="25" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="11.7109375" customWidth="1"/>
-    <col min="26" max="26" width="20.7109375" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" customWidth="1"/>
-    <col min="28" max="28" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="60.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.28515625" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" customWidth="1"/>
+    <col min="9" max="9" width="33.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="11.7109375" customWidth="1"/>
+    <col min="25" max="25" width="20.7109375" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" customWidth="1"/>
+    <col min="27" max="27" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>296</v>
       </c>
+      <c r="B2" t="s">
+        <v>202</v>
+      </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H2" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="J2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" t="s">
         <v>132</v>
       </c>
-      <c r="W2" t="s">
+      <c r="V2" t="s">
         <v>62</v>
       </c>
-      <c r="X2">
-        <v>34380047</v>
+      <c r="W2">
+        <v>34380047</v>
+      </c>
+      <c r="X2" t="s">
+        <v>29</v>
       </c>
       <c r="Y2" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z2" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA2" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>297</v>
       </c>
+      <c r="B3" t="s">
+        <v>203</v>
+      </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H3" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="J3" t="s">
-        <v>175</v>
-      </c>
-      <c r="K3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" t="s">
         <v>133</v>
       </c>
-      <c r="W3" t="s">
+      <c r="V3" t="s">
         <v>63</v>
       </c>
-      <c r="X3">
-        <v>34380047</v>
+      <c r="W3">
+        <v>34380047</v>
+      </c>
+      <c r="X3" t="s">
+        <v>29</v>
       </c>
       <c r="Y3" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z3" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA3" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>298</v>
       </c>
+      <c r="B4" t="s">
+        <v>204</v>
+      </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>175</v>
       </c>
       <c r="J4" t="s">
-        <v>175</v>
-      </c>
-      <c r="K4" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" t="s">
         <v>134</v>
       </c>
-      <c r="W4" t="s">
+      <c r="V4" t="s">
         <v>64</v>
       </c>
-      <c r="X4">
-        <v>34380047</v>
+      <c r="W4">
+        <v>34380047</v>
+      </c>
+      <c r="X4" t="s">
+        <v>29</v>
       </c>
       <c r="Y4" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z4" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA4" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB4" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>299</v>
       </c>
+      <c r="B5" t="s">
+        <v>363</v>
+      </c>
       <c r="C5" t="s">
-        <v>363</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H5" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="J5" t="s">
-        <v>189</v>
-      </c>
-      <c r="K5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" t="s">
         <v>135</v>
       </c>
-      <c r="W5" t="s">
+      <c r="V5" t="s">
         <v>65</v>
       </c>
-      <c r="X5">
-        <v>34380047</v>
+      <c r="W5">
+        <v>34380047</v>
+      </c>
+      <c r="X5" t="s">
+        <v>29</v>
       </c>
       <c r="Y5" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z5" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>300</v>
       </c>
+      <c r="B6" t="s">
+        <v>364</v>
+      </c>
       <c r="C6" t="s">
-        <v>364</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H6" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="J6" t="s">
-        <v>189</v>
-      </c>
-      <c r="K6" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" t="s">
         <v>136</v>
       </c>
-      <c r="W6" t="s">
+      <c r="V6" t="s">
         <v>66</v>
       </c>
-      <c r="X6">
-        <v>34380047</v>
+      <c r="W6">
+        <v>34380047</v>
+      </c>
+      <c r="X6" t="s">
+        <v>29</v>
       </c>
       <c r="Y6" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z6" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA6" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>301</v>
       </c>
+      <c r="B7" t="s">
+        <v>365</v>
+      </c>
       <c r="C7" t="s">
-        <v>365</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="J7" t="s">
-        <v>190</v>
-      </c>
-      <c r="K7" t="s">
-        <v>61</v>
-      </c>
-      <c r="M7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" t="s">
         <v>137</v>
       </c>
-      <c r="W7" t="s">
+      <c r="V7" t="s">
         <v>67</v>
       </c>
-      <c r="X7">
-        <v>34380047</v>
+      <c r="W7">
+        <v>34380047</v>
+      </c>
+      <c r="X7" t="s">
+        <v>29</v>
       </c>
       <c r="Y7" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z7" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA7" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB7" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>302</v>
       </c>
+      <c r="B8" t="s">
+        <v>366</v>
+      </c>
       <c r="C8" t="s">
-        <v>366</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="J8" t="s">
-        <v>190</v>
-      </c>
-      <c r="K8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" t="s">
         <v>138</v>
       </c>
-      <c r="W8" t="s">
+      <c r="V8" t="s">
         <v>68</v>
       </c>
-      <c r="X8">
-        <v>34380047</v>
+      <c r="W8">
+        <v>34380047</v>
+      </c>
+      <c r="X8" t="s">
+        <v>29</v>
       </c>
       <c r="Y8" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z8" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA8" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB8" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>303</v>
       </c>
+      <c r="B9" t="s">
+        <v>205</v>
+      </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H9" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="J9" t="s">
-        <v>176</v>
-      </c>
-      <c r="K9" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" t="s">
         <v>138</v>
       </c>
-      <c r="W9" t="s">
+      <c r="V9" t="s">
         <v>69</v>
       </c>
-      <c r="X9">
-        <v>34380047</v>
+      <c r="W9">
+        <v>34380047</v>
+      </c>
+      <c r="X9" t="s">
+        <v>29</v>
       </c>
       <c r="Y9" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z9" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA9" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB9" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>304</v>
       </c>
+      <c r="B10" t="s">
+        <v>206</v>
+      </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H10" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="J10" t="s">
-        <v>176</v>
-      </c>
-      <c r="K10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" t="s">
         <v>139</v>
       </c>
-      <c r="W10" t="s">
+      <c r="V10" t="s">
         <v>70</v>
       </c>
-      <c r="X10">
-        <v>34380047</v>
+      <c r="W10">
+        <v>34380047</v>
+      </c>
+      <c r="X10" t="s">
+        <v>29</v>
       </c>
       <c r="Y10" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z10" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA10" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB10" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>305</v>
       </c>
+      <c r="B11" t="s">
+        <v>207</v>
+      </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>176</v>
-      </c>
-      <c r="K11" t="s">
-        <v>61</v>
-      </c>
-      <c r="M11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" t="s">
         <v>140</v>
       </c>
-      <c r="W11" t="s">
+      <c r="V11" t="s">
         <v>71</v>
       </c>
-      <c r="X11">
-        <v>34380047</v>
+      <c r="W11">
+        <v>34380047</v>
+      </c>
+      <c r="X11" t="s">
+        <v>29</v>
       </c>
       <c r="Y11" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z11" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA11" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>306</v>
       </c>
+      <c r="B12" t="s">
+        <v>208</v>
+      </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H12" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I12" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>176</v>
-      </c>
-      <c r="K12" t="s">
-        <v>61</v>
-      </c>
-      <c r="M12" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" t="s">
         <v>141</v>
       </c>
-      <c r="W12" t="s">
+      <c r="V12" t="s">
         <v>72</v>
       </c>
-      <c r="X12">
-        <v>34380047</v>
+      <c r="W12">
+        <v>34380047</v>
+      </c>
+      <c r="X12" t="s">
+        <v>29</v>
       </c>
       <c r="Y12" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z12" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA12" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>307</v>
       </c>
+      <c r="B13" t="s">
+        <v>209</v>
+      </c>
       <c r="C13" t="s">
-        <v>209</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H13" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I13" t="s">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>176</v>
-      </c>
-      <c r="K13" t="s">
-        <v>61</v>
-      </c>
-      <c r="M13" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" t="s">
         <v>142</v>
       </c>
-      <c r="W13" t="s">
+      <c r="V13" t="s">
         <v>73</v>
       </c>
-      <c r="X13">
-        <v>34380047</v>
+      <c r="W13">
+        <v>34380047</v>
+      </c>
+      <c r="X13" t="s">
+        <v>29</v>
       </c>
       <c r="Y13" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z13" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA13" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB13" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>308</v>
       </c>
+      <c r="B14" t="s">
+        <v>210</v>
+      </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H14" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="J14" t="s">
-        <v>177</v>
-      </c>
-      <c r="K14" t="s">
-        <v>61</v>
-      </c>
-      <c r="M14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" t="s">
         <v>135</v>
       </c>
-      <c r="W14" t="s">
+      <c r="V14" t="s">
         <v>74</v>
       </c>
-      <c r="X14">
-        <v>34380047</v>
+      <c r="W14">
+        <v>34380047</v>
+      </c>
+      <c r="X14" t="s">
+        <v>29</v>
       </c>
       <c r="Y14" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z14" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA14" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB14" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>309</v>
       </c>
+      <c r="B15" t="s">
+        <v>211</v>
+      </c>
       <c r="C15" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H15" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="J15" t="s">
-        <v>177</v>
-      </c>
-      <c r="K15" t="s">
-        <v>61</v>
-      </c>
-      <c r="M15" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" t="s">
         <v>136</v>
       </c>
-      <c r="W15" t="s">
+      <c r="V15" t="s">
         <v>75</v>
       </c>
-      <c r="X15">
-        <v>34380047</v>
+      <c r="W15">
+        <v>34380047</v>
+      </c>
+      <c r="X15" t="s">
+        <v>29</v>
       </c>
       <c r="Y15" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z15" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA15" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>310</v>
       </c>
+      <c r="B16" t="s">
+        <v>212</v>
+      </c>
       <c r="C16" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H16" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="J16" t="s">
-        <v>177</v>
-      </c>
-      <c r="K16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" t="s">
         <v>143</v>
       </c>
-      <c r="W16" t="s">
+      <c r="V16" t="s">
         <v>76</v>
       </c>
-      <c r="X16">
-        <v>34380047</v>
+      <c r="W16">
+        <v>34380047</v>
+      </c>
+      <c r="X16" t="s">
+        <v>29</v>
       </c>
       <c r="Y16" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z16" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB16" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>311</v>
       </c>
+      <c r="B17" t="s">
+        <v>377</v>
+      </c>
       <c r="C17" t="s">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H17" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="J17" t="s">
-        <v>178</v>
-      </c>
-      <c r="K17" t="s">
-        <v>61</v>
-      </c>
-      <c r="M17" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" t="s">
         <v>137</v>
       </c>
-      <c r="W17" t="s">
+      <c r="V17" t="s">
         <v>77</v>
       </c>
-      <c r="X17">
-        <v>34380047</v>
+      <c r="W17">
+        <v>34380047</v>
+      </c>
+      <c r="X17" t="s">
+        <v>29</v>
       </c>
       <c r="Y17" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z17" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>312</v>
       </c>
+      <c r="B18" t="s">
+        <v>378</v>
+      </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H18" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I18" t="s">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="J18" t="s">
-        <v>178</v>
-      </c>
-      <c r="K18" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" t="s">
         <v>144</v>
       </c>
-      <c r="W18" t="s">
+      <c r="V18" t="s">
         <v>78</v>
       </c>
-      <c r="X18">
-        <v>34380047</v>
+      <c r="W18">
+        <v>34380047</v>
+      </c>
+      <c r="X18" t="s">
+        <v>29</v>
       </c>
       <c r="Y18" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z18" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA18" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB18" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>313</v>
       </c>
+      <c r="B19" t="s">
+        <v>379</v>
+      </c>
       <c r="C19" t="s">
-        <v>215</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H19" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="J19" t="s">
-        <v>178</v>
-      </c>
-      <c r="K19" t="s">
-        <v>61</v>
-      </c>
-      <c r="M19" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" t="s">
         <v>145</v>
       </c>
-      <c r="W19" t="s">
+      <c r="V19" t="s">
         <v>79</v>
       </c>
-      <c r="X19">
-        <v>34380047</v>
+      <c r="W19">
+        <v>34380047</v>
+      </c>
+      <c r="X19" t="s">
+        <v>29</v>
       </c>
       <c r="Y19" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z19" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB19" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>314</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="B20" t="s">
         <v>216</v>
       </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I20" t="s">
-        <v>28</v>
+        <v>179</v>
       </c>
       <c r="J20" t="s">
-        <v>179</v>
-      </c>
-      <c r="K20" t="s">
-        <v>61</v>
-      </c>
-      <c r="M20" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" t="s">
         <v>146</v>
       </c>
-      <c r="W20" t="s">
+      <c r="V20" t="s">
         <v>80</v>
       </c>
-      <c r="X20">
-        <v>34380047</v>
+      <c r="W20">
+        <v>34380047</v>
+      </c>
+      <c r="X20" t="s">
+        <v>29</v>
       </c>
       <c r="Y20" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z20" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA20" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB20" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="B21" t="s">
         <v>217</v>
       </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
       <c r="D21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G21" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H21" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>28</v>
+        <v>179</v>
       </c>
       <c r="J21" t="s">
-        <v>179</v>
-      </c>
-      <c r="K21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M21" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" t="s">
         <v>147</v>
       </c>
-      <c r="W21" t="s">
+      <c r="V21" t="s">
         <v>81</v>
       </c>
-      <c r="X21">
-        <v>34380047</v>
+      <c r="W21">
+        <v>34380047</v>
+      </c>
+      <c r="X21" t="s">
+        <v>29</v>
       </c>
       <c r="Y21" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z21" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA21" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB21" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>316</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="B22" t="s">
         <v>218</v>
       </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G22" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H22" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I22" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="J22" t="s">
-        <v>180</v>
-      </c>
-      <c r="K22" t="s">
-        <v>61</v>
-      </c>
-      <c r="M22" t="s">
+        <v>61</v>
+      </c>
+      <c r="L22" t="s">
         <v>148</v>
       </c>
-      <c r="W22" t="s">
+      <c r="V22" t="s">
         <v>82</v>
       </c>
-      <c r="X22">
-        <v>34380047</v>
+      <c r="W22">
+        <v>34380047</v>
+      </c>
+      <c r="X22" t="s">
+        <v>29</v>
       </c>
       <c r="Y22" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z22" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA22" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>317</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="B23" t="s">
         <v>219</v>
       </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H23" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I23" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="J23" t="s">
-        <v>180</v>
-      </c>
-      <c r="K23" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" t="s">
+        <v>61</v>
+      </c>
+      <c r="L23" t="s">
         <v>141</v>
       </c>
-      <c r="W23" t="s">
+      <c r="V23" t="s">
         <v>83</v>
       </c>
-      <c r="X23">
-        <v>34380047</v>
+      <c r="W23">
+        <v>34380047</v>
+      </c>
+      <c r="X23" t="s">
+        <v>29</v>
       </c>
       <c r="Y23" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z23" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA23" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB23" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>318</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="B24" t="s">
         <v>220</v>
       </c>
+      <c r="C24" t="s">
+        <v>58</v>
+      </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H24" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I24" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="J24" t="s">
-        <v>181</v>
-      </c>
-      <c r="K24" t="s">
-        <v>61</v>
-      </c>
-      <c r="M24" t="s">
+        <v>61</v>
+      </c>
+      <c r="L24" t="s">
         <v>149</v>
       </c>
-      <c r="W24" t="s">
+      <c r="V24" t="s">
         <v>84</v>
       </c>
-      <c r="X24">
-        <v>34380047</v>
+      <c r="W24">
+        <v>34380047</v>
+      </c>
+      <c r="X24" t="s">
+        <v>29</v>
       </c>
       <c r="Y24" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z24" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA24" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB24" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>319</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="B25" t="s">
         <v>221</v>
       </c>
+      <c r="C25" t="s">
+        <v>58</v>
+      </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E25" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H25" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I25" t="s">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="J25" t="s">
-        <v>181</v>
-      </c>
-      <c r="K25" t="s">
-        <v>61</v>
-      </c>
-      <c r="M25" t="s">
+        <v>61</v>
+      </c>
+      <c r="L25" t="s">
         <v>150</v>
       </c>
-      <c r="W25" t="s">
+      <c r="V25" t="s">
         <v>85</v>
       </c>
-      <c r="X25">
-        <v>34380047</v>
+      <c r="W25">
+        <v>34380047</v>
+      </c>
+      <c r="X25" t="s">
+        <v>29</v>
       </c>
       <c r="Y25" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z25" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA25" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB25" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>320</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="B26" t="s">
         <v>222</v>
       </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
       <c r="D26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F26" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G26" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H26" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="J26" t="s">
-        <v>182</v>
-      </c>
-      <c r="K26" t="s">
-        <v>61</v>
-      </c>
-      <c r="M26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" t="s">
         <v>196</v>
       </c>
-      <c r="W26" t="s">
+      <c r="V26" t="s">
         <v>86</v>
       </c>
-      <c r="X26">
-        <v>34380047</v>
+      <c r="W26">
+        <v>34380047</v>
+      </c>
+      <c r="X26" t="s">
+        <v>29</v>
       </c>
       <c r="Y26" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z26" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA26" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB26" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" t="s">
         <v>223</v>
       </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
       <c r="D27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G27" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H27" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I27" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="J27" t="s">
-        <v>183</v>
-      </c>
-      <c r="K27" t="s">
-        <v>61</v>
-      </c>
-      <c r="M27" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" t="s">
         <v>151</v>
       </c>
-      <c r="W27" t="s">
+      <c r="V27" t="s">
         <v>87</v>
       </c>
-      <c r="X27">
-        <v>34380047</v>
+      <c r="W27">
+        <v>34380047</v>
+      </c>
+      <c r="X27" t="s">
+        <v>29</v>
       </c>
       <c r="Y27" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z27" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA27" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB27" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>322</v>
       </c>
+      <c r="B28" t="s">
+        <v>224</v>
+      </c>
       <c r="C28" t="s">
-        <v>224</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I28" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="J28" t="s">
-        <v>184</v>
-      </c>
-      <c r="K28" t="s">
-        <v>61</v>
-      </c>
-      <c r="M28" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" t="s">
         <v>148</v>
       </c>
-      <c r="W28" t="s">
+      <c r="V28" t="s">
         <v>88</v>
       </c>
-      <c r="X28">
-        <v>34380047</v>
+      <c r="W28">
+        <v>34380047</v>
+      </c>
+      <c r="X28" t="s">
+        <v>29</v>
       </c>
       <c r="Y28" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z28" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA28" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB28" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>323</v>
       </c>
+      <c r="B29" t="s">
+        <v>225</v>
+      </c>
       <c r="C29" t="s">
-        <v>225</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="J29" t="s">
-        <v>184</v>
-      </c>
-      <c r="K29" t="s">
-        <v>61</v>
-      </c>
-      <c r="M29" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" t="s">
         <v>148</v>
       </c>
-      <c r="W29" t="s">
+      <c r="V29" t="s">
         <v>89</v>
       </c>
-      <c r="X29">
-        <v>34380047</v>
+      <c r="W29">
+        <v>34380047</v>
+      </c>
+      <c r="X29" t="s">
+        <v>29</v>
       </c>
       <c r="Y29" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z29" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA29" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB29" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>324</v>
       </c>
+      <c r="B30" t="s">
+        <v>226</v>
+      </c>
       <c r="C30" t="s">
-        <v>226</v>
+        <v>58</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F30" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G30" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H30" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I30" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="J30" t="s">
-        <v>184</v>
-      </c>
-      <c r="K30" t="s">
-        <v>61</v>
-      </c>
-      <c r="M30" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" t="s">
         <v>152</v>
       </c>
-      <c r="W30" t="s">
+      <c r="V30" t="s">
         <v>90</v>
       </c>
-      <c r="X30">
-        <v>34380047</v>
+      <c r="W30">
+        <v>34380047</v>
+      </c>
+      <c r="X30" t="s">
+        <v>29</v>
       </c>
       <c r="Y30" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z30" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA30" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB30" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>325</v>
       </c>
+      <c r="B31" t="s">
+        <v>227</v>
+      </c>
       <c r="C31" t="s">
-        <v>227</v>
+        <v>58</v>
       </c>
       <c r="D31" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E31" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G31" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H31" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I31" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="J31" t="s">
-        <v>184</v>
-      </c>
-      <c r="K31" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" t="s">
         <v>146</v>
       </c>
-      <c r="W31" t="s">
+      <c r="V31" t="s">
         <v>91</v>
       </c>
-      <c r="X31">
-        <v>34380047</v>
+      <c r="W31">
+        <v>34380047</v>
+      </c>
+      <c r="X31" t="s">
+        <v>29</v>
       </c>
       <c r="Y31" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z31" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA31" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB31" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>326</v>
       </c>
+      <c r="B32" t="s">
+        <v>228</v>
+      </c>
       <c r="C32" t="s">
-        <v>228</v>
+        <v>58</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F32" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G32" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H32" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I32" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="J32" t="s">
-        <v>185</v>
-      </c>
-      <c r="K32" t="s">
-        <v>61</v>
-      </c>
-      <c r="M32" t="s">
+        <v>61</v>
+      </c>
+      <c r="L32" t="s">
         <v>142</v>
       </c>
-      <c r="W32" t="s">
+      <c r="V32" t="s">
         <v>92</v>
       </c>
-      <c r="X32">
-        <v>34380047</v>
+      <c r="W32">
+        <v>34380047</v>
+      </c>
+      <c r="X32" t="s">
+        <v>29</v>
       </c>
       <c r="Y32" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z32" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA32" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB32" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>327</v>
       </c>
+      <c r="B33" t="s">
+        <v>229</v>
+      </c>
       <c r="C33" t="s">
-        <v>229</v>
+        <v>58</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H33" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I33" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="J33" t="s">
-        <v>185</v>
-      </c>
-      <c r="K33" t="s">
-        <v>61</v>
-      </c>
-      <c r="M33" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" t="s">
         <v>152</v>
       </c>
-      <c r="W33" t="s">
+      <c r="V33" t="s">
         <v>93</v>
       </c>
-      <c r="X33">
-        <v>34380047</v>
+      <c r="W33">
+        <v>34380047</v>
+      </c>
+      <c r="X33" t="s">
+        <v>29</v>
       </c>
       <c r="Y33" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z33" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA33" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB33" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>328</v>
       </c>
+      <c r="B34" t="s">
+        <v>230</v>
+      </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>58</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F34" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G34" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H34" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I34" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="J34" t="s">
-        <v>185</v>
-      </c>
-      <c r="K34" t="s">
-        <v>61</v>
-      </c>
-      <c r="M34" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" t="s">
         <v>147</v>
       </c>
-      <c r="W34" t="s">
+      <c r="V34" t="s">
         <v>94</v>
       </c>
-      <c r="X34">
-        <v>34380047</v>
+      <c r="W34">
+        <v>34380047</v>
+      </c>
+      <c r="X34" t="s">
+        <v>29</v>
       </c>
       <c r="Y34" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z34" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA34" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB34" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>329</v>
       </c>
+      <c r="B35" t="s">
+        <v>231</v>
+      </c>
       <c r="C35" t="s">
-        <v>231</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E35" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G35" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H35" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I35" t="s">
-        <v>28</v>
+        <v>185</v>
       </c>
       <c r="J35" t="s">
-        <v>185</v>
-      </c>
-      <c r="K35" t="s">
-        <v>61</v>
-      </c>
-      <c r="M35" t="s">
+        <v>61</v>
+      </c>
+      <c r="L35" t="s">
         <v>149</v>
       </c>
-      <c r="W35" t="s">
+      <c r="V35" t="s">
         <v>95</v>
       </c>
-      <c r="X35">
-        <v>34380047</v>
+      <c r="W35">
+        <v>34380047</v>
+      </c>
+      <c r="X35" t="s">
+        <v>29</v>
       </c>
       <c r="Y35" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z35" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA35" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB35" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>330</v>
       </c>
+      <c r="B36" t="s">
+        <v>232</v>
+      </c>
       <c r="C36" t="s">
-        <v>232</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="H36" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="I36" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="J36" t="s">
-        <v>186</v>
-      </c>
-      <c r="K36" t="s">
-        <v>61</v>
-      </c>
-      <c r="M36" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" t="s">
         <v>200</v>
       </c>
-      <c r="W36" t="s">
+      <c r="V36" t="s">
         <v>96</v>
       </c>
-      <c r="X36">
-        <v>34380047</v>
+      <c r="W36">
+        <v>34380047</v>
+      </c>
+      <c r="X36" t="s">
+        <v>29</v>
       </c>
       <c r="Y36" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z36" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA36" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB36" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>331</v>
       </c>
+      <c r="B37" t="s">
+        <v>233</v>
+      </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>58</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E37" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="H37" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="I37" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="J37" t="s">
-        <v>186</v>
-      </c>
-      <c r="K37" t="s">
-        <v>61</v>
-      </c>
-      <c r="M37" t="s">
+        <v>61</v>
+      </c>
+      <c r="L37" t="s">
         <v>199</v>
       </c>
-      <c r="W37" t="s">
+      <c r="V37" t="s">
         <v>97</v>
       </c>
-      <c r="X37">
-        <v>34380047</v>
+      <c r="W37">
+        <v>34380047</v>
+      </c>
+      <c r="X37" t="s">
+        <v>29</v>
       </c>
       <c r="Y37" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z37" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA37" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB37" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>332</v>
       </c>
+      <c r="B38" t="s">
+        <v>234</v>
+      </c>
       <c r="C38" t="s">
-        <v>234</v>
+        <v>58</v>
       </c>
       <c r="D38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E38" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G38" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H38" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I38" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="J38" t="s">
-        <v>187</v>
-      </c>
-      <c r="K38" t="s">
-        <v>61</v>
-      </c>
-      <c r="M38" t="s">
+        <v>61</v>
+      </c>
+      <c r="L38" t="s">
         <v>142</v>
       </c>
-      <c r="W38" t="s">
+      <c r="V38" t="s">
         <v>98</v>
       </c>
-      <c r="X38">
-        <v>34380047</v>
+      <c r="W38">
+        <v>34380047</v>
+      </c>
+      <c r="X38" t="s">
+        <v>29</v>
       </c>
       <c r="Y38" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z38" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA38" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB38" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>333</v>
       </c>
+      <c r="B39" t="s">
+        <v>235</v>
+      </c>
       <c r="C39" t="s">
-        <v>235</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H39" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I39" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="J39" t="s">
-        <v>187</v>
-      </c>
-      <c r="K39" t="s">
-        <v>61</v>
-      </c>
-      <c r="M39" t="s">
+        <v>61</v>
+      </c>
+      <c r="L39" t="s">
         <v>141</v>
       </c>
-      <c r="W39" t="s">
+      <c r="V39" t="s">
         <v>99</v>
       </c>
-      <c r="X39">
-        <v>34380047</v>
+      <c r="W39">
+        <v>34380047</v>
+      </c>
+      <c r="X39" t="s">
+        <v>29</v>
       </c>
       <c r="Y39" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z39" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA39" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB39" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>334</v>
       </c>
+      <c r="B40" t="s">
+        <v>236</v>
+      </c>
       <c r="C40" t="s">
-        <v>236</v>
+        <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E40" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H40" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="J40" t="s">
-        <v>187</v>
-      </c>
-      <c r="K40" t="s">
-        <v>61</v>
-      </c>
-      <c r="M40" t="s">
+        <v>61</v>
+      </c>
+      <c r="L40" t="s">
         <v>153</v>
       </c>
-      <c r="W40" t="s">
+      <c r="V40" t="s">
         <v>100</v>
       </c>
-      <c r="X40">
-        <v>34380047</v>
+      <c r="W40">
+        <v>34380047</v>
+      </c>
+      <c r="X40" t="s">
+        <v>29</v>
       </c>
       <c r="Y40" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z40" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA40" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB40" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>335</v>
       </c>
+      <c r="B41" t="s">
+        <v>237</v>
+      </c>
       <c r="C41" t="s">
-        <v>237</v>
+        <v>58</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E41" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H41" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="J41" t="s">
-        <v>187</v>
-      </c>
-      <c r="K41" t="s">
-        <v>61</v>
-      </c>
-      <c r="M41" t="s">
+        <v>61</v>
+      </c>
+      <c r="L41" t="s">
         <v>154</v>
       </c>
-      <c r="W41" t="s">
+      <c r="V41" t="s">
         <v>101</v>
       </c>
-      <c r="X41">
-        <v>34380047</v>
+      <c r="W41">
+        <v>34380047</v>
+      </c>
+      <c r="X41" t="s">
+        <v>29</v>
       </c>
       <c r="Y41" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z41" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA41" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB41" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>336</v>
       </c>
+      <c r="B42" t="s">
+        <v>238</v>
+      </c>
       <c r="C42" t="s">
-        <v>238</v>
+        <v>58</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E42" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G42" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H42" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I42" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="J42" t="s">
-        <v>188</v>
-      </c>
-      <c r="K42" t="s">
-        <v>61</v>
-      </c>
-      <c r="M42" t="s">
+        <v>61</v>
+      </c>
+      <c r="L42" t="s">
         <v>142</v>
       </c>
-      <c r="W42" t="s">
+      <c r="V42" t="s">
         <v>102</v>
       </c>
-      <c r="X42">
-        <v>34380047</v>
+      <c r="W42">
+        <v>34380047</v>
+      </c>
+      <c r="X42" t="s">
+        <v>29</v>
       </c>
       <c r="Y42" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z42" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA42" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB42" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>337</v>
       </c>
+      <c r="B43" t="s">
+        <v>239</v>
+      </c>
       <c r="C43" t="s">
-        <v>239</v>
+        <v>58</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E43" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G43" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H43" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I43" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="J43" t="s">
-        <v>188</v>
-      </c>
-      <c r="K43" t="s">
-        <v>61</v>
-      </c>
-      <c r="M43" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" t="s">
         <v>141</v>
       </c>
-      <c r="W43" t="s">
+      <c r="V43" t="s">
         <v>103</v>
       </c>
-      <c r="X43">
-        <v>34380047</v>
+      <c r="W43">
+        <v>34380047</v>
+      </c>
+      <c r="X43" t="s">
+        <v>29</v>
       </c>
       <c r="Y43" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z43" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA43" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB43" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>338</v>
       </c>
+      <c r="B44" t="s">
+        <v>240</v>
+      </c>
       <c r="C44" t="s">
-        <v>240</v>
+        <v>58</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G44" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H44" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I44" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="J44" t="s">
-        <v>188</v>
-      </c>
-      <c r="K44" t="s">
-        <v>61</v>
-      </c>
-      <c r="M44" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" t="s">
         <v>134</v>
       </c>
-      <c r="W44" t="s">
+      <c r="V44" t="s">
         <v>104</v>
       </c>
-      <c r="X44">
-        <v>34380047</v>
+      <c r="W44">
+        <v>34380047</v>
+      </c>
+      <c r="X44" t="s">
+        <v>29</v>
       </c>
       <c r="Y44" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z44" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA44" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB44" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>339</v>
       </c>
+      <c r="B45" t="s">
+        <v>241</v>
+      </c>
       <c r="C45" t="s">
-        <v>241</v>
+        <v>58</v>
       </c>
       <c r="D45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E45" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F45" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G45" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H45" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="J45" t="s">
-        <v>188</v>
-      </c>
-      <c r="K45" t="s">
-        <v>61</v>
-      </c>
-      <c r="M45" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" t="s">
         <v>155</v>
       </c>
-      <c r="W45" t="s">
+      <c r="V45" t="s">
         <v>105</v>
       </c>
-      <c r="X45">
-        <v>34380047</v>
+      <c r="W45">
+        <v>34380047</v>
+      </c>
+      <c r="X45" t="s">
+        <v>29</v>
       </c>
       <c r="Y45" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z45" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA45" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB45" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>340</v>
       </c>
+      <c r="B46" t="s">
+        <v>367</v>
+      </c>
       <c r="C46" t="s">
-        <v>367</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G46" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H46" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I46" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="J46" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" t="s">
+        <v>197</v>
+      </c>
+      <c r="V46" t="s">
+        <v>106</v>
+      </c>
+      <c r="W46">
+        <v>34380047</v>
+      </c>
+      <c r="X46" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>362</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA46" t="s">
         <v>170</v>
       </c>
-      <c r="K46" t="s">
-        <v>61</v>
-      </c>
-      <c r="M46" t="s">
-        <v>197</v>
-      </c>
-      <c r="W46" t="s">
-        <v>106</v>
-      </c>
-      <c r="X46">
-        <v>34380047</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z46" t="s">
-        <v>362</v>
-      </c>
-      <c r="AA46" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB46" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>341</v>
       </c>
+      <c r="B47" t="s">
+        <v>368</v>
+      </c>
       <c r="C47" t="s">
-        <v>368</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E47" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F47" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H47" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I47" t="s">
-        <v>28</v>
+        <v>171</v>
       </c>
       <c r="J47" t="s">
+        <v>61</v>
+      </c>
+      <c r="L47" t="s">
+        <v>198</v>
+      </c>
+      <c r="V47" t="s">
+        <v>107</v>
+      </c>
+      <c r="W47">
+        <v>34380047</v>
+      </c>
+      <c r="X47" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>362</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA47" t="s">
         <v>171</v>
       </c>
-      <c r="K47" t="s">
-        <v>61</v>
-      </c>
-      <c r="M47" t="s">
-        <v>198</v>
-      </c>
-      <c r="W47" t="s">
-        <v>107</v>
-      </c>
-      <c r="X47">
-        <v>34380047</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>362</v>
-      </c>
-      <c r="AA47" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>342</v>
       </c>
+      <c r="B48" t="s">
+        <v>369</v>
+      </c>
       <c r="C48" t="s">
-        <v>369</v>
+        <v>58</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G48" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H48" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="J48" t="s">
-        <v>162</v>
-      </c>
-      <c r="K48" t="s">
-        <v>61</v>
-      </c>
-      <c r="M48" t="s">
+        <v>61</v>
+      </c>
+      <c r="L48" t="s">
         <v>139</v>
       </c>
-      <c r="W48" t="s">
+      <c r="V48" t="s">
         <v>108</v>
       </c>
-      <c r="X48">
-        <v>34380047</v>
+      <c r="W48">
+        <v>34380047</v>
+      </c>
+      <c r="X48" t="s">
+        <v>29</v>
       </c>
       <c r="Y48" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z48" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA48" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB48" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>343</v>
       </c>
+      <c r="B49" t="s">
+        <v>370</v>
+      </c>
       <c r="C49" t="s">
-        <v>370</v>
+        <v>58</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E49" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G49" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H49" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I49" t="s">
-        <v>28</v>
+        <v>191</v>
       </c>
       <c r="J49" t="s">
-        <v>191</v>
-      </c>
-      <c r="K49" t="s">
-        <v>61</v>
-      </c>
-      <c r="M49" t="s">
+        <v>61</v>
+      </c>
+      <c r="L49" t="s">
         <v>144</v>
       </c>
-      <c r="W49" t="s">
+      <c r="V49" t="s">
         <v>109</v>
       </c>
-      <c r="X49">
-        <v>34380047</v>
+      <c r="W49">
+        <v>34380047</v>
+      </c>
+      <c r="X49" t="s">
+        <v>29</v>
       </c>
       <c r="Y49" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z49" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA49" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB49" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>344</v>
       </c>
+      <c r="B50" t="s">
+        <v>371</v>
+      </c>
       <c r="C50" t="s">
-        <v>371</v>
+        <v>58</v>
       </c>
       <c r="D50" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E50" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G50" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H50" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I50" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="J50" t="s">
+        <v>61</v>
+      </c>
+      <c r="L50" t="s">
+        <v>134</v>
+      </c>
+      <c r="V50" t="s">
+        <v>110</v>
+      </c>
+      <c r="W50">
+        <v>34380047</v>
+      </c>
+      <c r="X50" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>362</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA50" t="s">
         <v>164</v>
       </c>
-      <c r="K50" t="s">
-        <v>61</v>
-      </c>
-      <c r="M50" t="s">
-        <v>134</v>
-      </c>
-      <c r="W50" t="s">
-        <v>110</v>
-      </c>
-      <c r="X50">
-        <v>34380047</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>362</v>
-      </c>
-      <c r="AA50" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>345</v>
       </c>
+      <c r="B51" t="s">
+        <v>372</v>
+      </c>
       <c r="C51" t="s">
-        <v>372</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E51" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G51" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H51" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I51" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="J51" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" t="s">
+        <v>143</v>
+      </c>
+      <c r="V51" t="s">
+        <v>111</v>
+      </c>
+      <c r="W51">
+        <v>34380047</v>
+      </c>
+      <c r="X51" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>362</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA51" t="s">
         <v>164</v>
       </c>
-      <c r="K51" t="s">
-        <v>61</v>
-      </c>
-      <c r="M51" t="s">
-        <v>143</v>
-      </c>
-      <c r="W51" t="s">
-        <v>111</v>
-      </c>
-      <c r="X51">
-        <v>34380047</v>
-      </c>
-      <c r="Y51" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>362</v>
-      </c>
-      <c r="AA51" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB51" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>346</v>
       </c>
+      <c r="B52" t="s">
+        <v>242</v>
+      </c>
       <c r="C52" t="s">
-        <v>242</v>
+        <v>58</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E52" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F52" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G52" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H52" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I52" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="J52" t="s">
-        <v>192</v>
-      </c>
-      <c r="K52" t="s">
-        <v>61</v>
-      </c>
-      <c r="M52" t="s">
+        <v>61</v>
+      </c>
+      <c r="L52" t="s">
         <v>142</v>
       </c>
-      <c r="W52" t="s">
+      <c r="V52" t="s">
         <v>112</v>
       </c>
-      <c r="X52">
-        <v>34380047</v>
+      <c r="W52">
+        <v>34380047</v>
+      </c>
+      <c r="X52" t="s">
+        <v>29</v>
       </c>
       <c r="Y52" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z52" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA52" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB52" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>347</v>
       </c>
+      <c r="B53" t="s">
+        <v>243</v>
+      </c>
       <c r="C53" t="s">
-        <v>243</v>
+        <v>58</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E53" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F53" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G53" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H53" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I53" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="J53" t="s">
-        <v>192</v>
-      </c>
-      <c r="K53" t="s">
-        <v>61</v>
-      </c>
-      <c r="M53" t="s">
+        <v>61</v>
+      </c>
+      <c r="L53" t="s">
         <v>152</v>
       </c>
-      <c r="W53" t="s">
+      <c r="V53" t="s">
         <v>113</v>
       </c>
-      <c r="X53">
-        <v>34380047</v>
+      <c r="W53">
+        <v>34380047</v>
+      </c>
+      <c r="X53" t="s">
+        <v>29</v>
       </c>
       <c r="Y53" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z53" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA53" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB53" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>348</v>
       </c>
+      <c r="B54" t="s">
+        <v>244</v>
+      </c>
       <c r="C54" t="s">
-        <v>244</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E54" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F54" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G54" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H54" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I54" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="J54" t="s">
-        <v>192</v>
-      </c>
-      <c r="K54" t="s">
-        <v>61</v>
-      </c>
-      <c r="M54" t="s">
+        <v>61</v>
+      </c>
+      <c r="L54" t="s">
         <v>140</v>
       </c>
-      <c r="W54" t="s">
+      <c r="V54" t="s">
         <v>114</v>
       </c>
-      <c r="X54">
-        <v>34380047</v>
+      <c r="W54">
+        <v>34380047</v>
+      </c>
+      <c r="X54" t="s">
+        <v>29</v>
       </c>
       <c r="Y54" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z54" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA54" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB54" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>349</v>
       </c>
+      <c r="B55" t="s">
+        <v>245</v>
+      </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="D55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E55" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F55" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G55" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H55" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I55" t="s">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="J55" t="s">
-        <v>192</v>
-      </c>
-      <c r="K55" t="s">
-        <v>61</v>
-      </c>
-      <c r="M55" t="s">
+        <v>61</v>
+      </c>
+      <c r="L55" t="s">
         <v>145</v>
       </c>
-      <c r="W55" t="s">
+      <c r="V55" t="s">
         <v>115</v>
       </c>
-      <c r="X55">
-        <v>34380047</v>
+      <c r="W55">
+        <v>34380047</v>
+      </c>
+      <c r="X55" t="s">
+        <v>29</v>
       </c>
       <c r="Y55" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z55" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA55" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB55" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>350</v>
       </c>
+      <c r="B56" t="s">
+        <v>246</v>
+      </c>
       <c r="C56" t="s">
-        <v>246</v>
+        <v>58</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E56" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G56" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H56" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I56" t="s">
-        <v>28</v>
+        <v>193</v>
       </c>
       <c r="J56" t="s">
-        <v>193</v>
-      </c>
-      <c r="K56" t="s">
-        <v>61</v>
-      </c>
-      <c r="M56" t="s">
+        <v>61</v>
+      </c>
+      <c r="L56" t="s">
         <v>152</v>
       </c>
-      <c r="W56" t="s">
+      <c r="V56" t="s">
         <v>116</v>
       </c>
-      <c r="X56">
-        <v>34380047</v>
+      <c r="W56">
+        <v>34380047</v>
+      </c>
+      <c r="X56" t="s">
+        <v>29</v>
       </c>
       <c r="Y56" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z56" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA56" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB56" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>351</v>
       </c>
+      <c r="B57" t="s">
+        <v>247</v>
+      </c>
       <c r="C57" t="s">
-        <v>247</v>
+        <v>58</v>
       </c>
       <c r="D57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G57" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H57" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I57" t="s">
-        <v>28</v>
+        <v>193</v>
       </c>
       <c r="J57" t="s">
-        <v>193</v>
-      </c>
-      <c r="K57" t="s">
-        <v>61</v>
-      </c>
-      <c r="M57" t="s">
+        <v>61</v>
+      </c>
+      <c r="L57" t="s">
         <v>141</v>
       </c>
-      <c r="W57" t="s">
+      <c r="V57" t="s">
         <v>117</v>
       </c>
-      <c r="X57">
-        <v>34380047</v>
+      <c r="W57">
+        <v>34380047</v>
+      </c>
+      <c r="X57" t="s">
+        <v>29</v>
       </c>
       <c r="Y57" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z57" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA57" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB57" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>352</v>
       </c>
+      <c r="B58" t="s">
+        <v>248</v>
+      </c>
       <c r="C58" t="s">
-        <v>248</v>
+        <v>58</v>
       </c>
       <c r="D58" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E58" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G58" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H58" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>28</v>
+        <v>193</v>
       </c>
       <c r="J58" t="s">
-        <v>193</v>
-      </c>
-      <c r="K58" t="s">
-        <v>61</v>
-      </c>
-      <c r="M58" t="s">
+        <v>61</v>
+      </c>
+      <c r="L58" t="s">
         <v>150</v>
       </c>
-      <c r="W58" t="s">
+      <c r="V58" t="s">
         <v>118</v>
       </c>
-      <c r="X58">
-        <v>34380047</v>
+      <c r="W58">
+        <v>34380047</v>
+      </c>
+      <c r="X58" t="s">
+        <v>29</v>
       </c>
       <c r="Y58" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z58" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA58" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB58" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>353</v>
       </c>
+      <c r="B59" t="s">
+        <v>249</v>
+      </c>
       <c r="C59" t="s">
-        <v>249</v>
+        <v>58</v>
       </c>
       <c r="D59" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E59" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G59" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H59" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I59" t="s">
-        <v>28</v>
+        <v>193</v>
       </c>
       <c r="J59" t="s">
-        <v>193</v>
-      </c>
-      <c r="K59" t="s">
-        <v>61</v>
-      </c>
-      <c r="M59" t="s">
+        <v>61</v>
+      </c>
+      <c r="L59" t="s">
         <v>156</v>
       </c>
-      <c r="W59" t="s">
+      <c r="V59" t="s">
         <v>119</v>
       </c>
-      <c r="X59">
-        <v>34380047</v>
+      <c r="W59">
+        <v>34380047</v>
+      </c>
+      <c r="X59" t="s">
+        <v>29</v>
       </c>
       <c r="Y59" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z59" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA59" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB59" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>354</v>
       </c>
+      <c r="B60" t="s">
+        <v>250</v>
+      </c>
       <c r="C60" t="s">
-        <v>250</v>
+        <v>58</v>
       </c>
       <c r="D60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E60" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F60" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G60" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H60" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I60" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="J60" t="s">
-        <v>194</v>
-      </c>
-      <c r="K60" t="s">
-        <v>61</v>
-      </c>
-      <c r="M60" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" t="s">
         <v>151</v>
       </c>
-      <c r="W60" t="s">
+      <c r="V60" t="s">
         <v>120</v>
       </c>
-      <c r="X60">
-        <v>34380047</v>
+      <c r="W60">
+        <v>34380047</v>
+      </c>
+      <c r="X60" t="s">
+        <v>29</v>
       </c>
       <c r="Y60" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z60" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA60" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB60" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>355</v>
       </c>
+      <c r="B61" t="s">
+        <v>251</v>
+      </c>
       <c r="C61" t="s">
-        <v>251</v>
+        <v>58</v>
       </c>
       <c r="D61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E61" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F61" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G61" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H61" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I61" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="J61" t="s">
-        <v>194</v>
-      </c>
-      <c r="K61" t="s">
-        <v>61</v>
-      </c>
-      <c r="M61" t="s">
+        <v>61</v>
+      </c>
+      <c r="L61" t="s">
         <v>148</v>
       </c>
-      <c r="W61" t="s">
+      <c r="V61" t="s">
         <v>121</v>
       </c>
-      <c r="X61">
-        <v>34380047</v>
+      <c r="W61">
+        <v>34380047</v>
+      </c>
+      <c r="X61" t="s">
+        <v>29</v>
       </c>
       <c r="Y61" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z61" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA61" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB61" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>356</v>
       </c>
+      <c r="B62" t="s">
+        <v>252</v>
+      </c>
       <c r="C62" t="s">
-        <v>252</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E62" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F62" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G62" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H62" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I62" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="J62" t="s">
-        <v>194</v>
-      </c>
-      <c r="K62" t="s">
-        <v>61</v>
-      </c>
-      <c r="M62" t="s">
+        <v>61</v>
+      </c>
+      <c r="L62" t="s">
         <v>151</v>
       </c>
-      <c r="W62" t="s">
+      <c r="V62" t="s">
         <v>122</v>
       </c>
-      <c r="X62">
-        <v>34380047</v>
+      <c r="W62">
+        <v>34380047</v>
+      </c>
+      <c r="X62" t="s">
+        <v>29</v>
       </c>
       <c r="Y62" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z62" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA62" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB62" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>357</v>
       </c>
+      <c r="B63" t="s">
+        <v>253</v>
+      </c>
       <c r="C63" t="s">
-        <v>253</v>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E63" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F63" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G63" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H63" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="I63" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="J63" t="s">
-        <v>194</v>
-      </c>
-      <c r="K63" t="s">
-        <v>61</v>
-      </c>
-      <c r="M63" t="s">
+        <v>61</v>
+      </c>
+      <c r="L63" t="s">
         <v>141</v>
       </c>
-      <c r="W63" t="s">
+      <c r="V63" t="s">
         <v>123</v>
       </c>
-      <c r="X63">
-        <v>34380047</v>
+      <c r="W63">
+        <v>34380047</v>
+      </c>
+      <c r="X63" t="s">
+        <v>29</v>
       </c>
       <c r="Y63" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z63" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA63" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB63" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>358</v>
       </c>
+      <c r="B64" t="s">
+        <v>373</v>
+      </c>
       <c r="C64" t="s">
-        <v>373</v>
+        <v>58</v>
       </c>
       <c r="D64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E64" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F64" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G64" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H64" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I64" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="J64" t="s">
-        <v>195</v>
-      </c>
-      <c r="K64" t="s">
-        <v>61</v>
-      </c>
-      <c r="M64" t="s">
+        <v>61</v>
+      </c>
+      <c r="L64" t="s">
         <v>132</v>
       </c>
-      <c r="W64" t="s">
+      <c r="V64" t="s">
         <v>124</v>
       </c>
-      <c r="X64">
-        <v>34380047</v>
+      <c r="W64">
+        <v>34380047</v>
+      </c>
+      <c r="X64" t="s">
+        <v>29</v>
       </c>
       <c r="Y64" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z64" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA64" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB64" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>359</v>
       </c>
+      <c r="B65" t="s">
+        <v>374</v>
+      </c>
       <c r="C65" t="s">
-        <v>374</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E65" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F65" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G65" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H65" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I65" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="J65" t="s">
-        <v>195</v>
-      </c>
-      <c r="K65" t="s">
-        <v>61</v>
-      </c>
-      <c r="M65" t="s">
+        <v>61</v>
+      </c>
+      <c r="L65" t="s">
         <v>133</v>
       </c>
-      <c r="W65" t="s">
+      <c r="V65" t="s">
         <v>125</v>
       </c>
-      <c r="X65">
-        <v>34380047</v>
+      <c r="W65">
+        <v>34380047</v>
+      </c>
+      <c r="X65" t="s">
+        <v>29</v>
       </c>
       <c r="Y65" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z65" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA65" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB65" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>360</v>
       </c>
+      <c r="B66" t="s">
+        <v>375</v>
+      </c>
       <c r="C66" t="s">
-        <v>375</v>
+        <v>58</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E66" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F66" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G66" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H66" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="J66" t="s">
+        <v>61</v>
+      </c>
+      <c r="L66" t="s">
+        <v>157</v>
+      </c>
+      <c r="V66" t="s">
+        <v>126</v>
+      </c>
+      <c r="W66">
+        <v>34380047</v>
+      </c>
+      <c r="X66" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>362</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA66" t="s">
         <v>174</v>
       </c>
-      <c r="K66" t="s">
-        <v>61</v>
-      </c>
-      <c r="M66" t="s">
-        <v>157</v>
-      </c>
-      <c r="W66" t="s">
-        <v>126</v>
-      </c>
-      <c r="X66">
-        <v>34380047</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>362</v>
-      </c>
-      <c r="AA66" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB66" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>361</v>
       </c>
+      <c r="B67" t="s">
+        <v>376</v>
+      </c>
       <c r="C67" t="s">
-        <v>376</v>
+        <v>58</v>
       </c>
       <c r="D67" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E67" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="F67" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>60</v>
+        <v>131</v>
       </c>
       <c r="H67" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="I67" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="J67" t="s">
-        <v>174</v>
-      </c>
-      <c r="K67" t="s">
-        <v>61</v>
-      </c>
-      <c r="M67" t="s">
+        <v>61</v>
+      </c>
+      <c r="L67" t="s">
         <v>158</v>
       </c>
-      <c r="W67" t="s">
+      <c r="V67" t="s">
         <v>127</v>
       </c>
-      <c r="X67">
-        <v>34380047</v>
+      <c r="W67">
+        <v>34380047</v>
+      </c>
+      <c r="X67" t="s">
+        <v>29</v>
       </c>
       <c r="Y67" t="s">
-        <v>29</v>
+        <v>362</v>
       </c>
       <c r="Z67" t="s">
-        <v>362</v>
+        <v>201</v>
       </c>
       <c r="AA67" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB67" t="s">
         <v>174</v>
       </c>
     </row>
